--- a/registration_forms/042_dust_control_training_registration_form--registration_forms.xlsx
+++ b/registration_forms/042_dust_control_training_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'contractor'}</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Contractor'}</t>
+          <t>Contractor</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'i_have_read,_understand,_and_agree_to_the_terms_and_conditions'}</t>
+          <t>i_have_read,_understand,_and_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'I have read, understand, and agree to the terms and conditions'}</t>
+          <t>I have read, understand, and agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'i_have_not_read,_do_not_understand,_and_do_not_agree_to_the_terms_and_conditions'}</t>
+          <t>i_have_not_read,_do_not_understand,_and_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'I have not read, do not understand, and do not agree to the terms and conditions'}</t>
+          <t>I have not read, do not understand, and do not agree to the terms and conditions</t>
         </is>
       </c>
     </row>
